--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.10.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T07:51:53+00:00</t>
+    <t>2023-12-21T16:22:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.0</t>
+    <t>0.11.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T16:22:28+00:00</t>
+    <t>2023-12-28T09:08:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.11.0</t>
+    <t>0.12.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-28T09:08:39+00:00</t>
+    <t>2023-12-29T17:54:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.12.0</t>
+    <t>0.13.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-29T17:54:36+00:00</t>
+    <t>2024-01-03T19:41:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA TIU DOCUMENT (file 8925) to FHIR Binary</t>
+    <t>This StructureDefinition contains the maps for VistA file TIU DOCUMENT (#8925) to Binary</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -9,11 +9,14 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$9</definedName>
+  </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="133">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.13.0</t>
+    <t>0.14.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -42,7 +45,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Document Reference {Binary}</t>
+    <t>Document Reference Binary</t>
   </si>
   <si>
     <t>Status</t>
@@ -57,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-03T19:41:50+00:00</t>
+    <t>2024-01-13T13:47:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -376,10 +379,6 @@
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/mimetypes|4.0.1</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-5:++: fixed value = text/plain {null}</t>
   </si>
   <si>
     <t>ED.mediaType</t>
@@ -555,6 +554,21 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color indexed="22"/>
+        <i val="true"/>
+      </font>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -886,7 +900,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
         <v>30</v>
       </c>
@@ -994,7 +1008,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
         <v>83</v>
       </c>
@@ -1102,7 +1116,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
         <v>91</v>
       </c>
@@ -1208,7 +1222,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
         <v>97</v>
       </c>
@@ -1316,7 +1330,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
         <v>103</v>
       </c>
@@ -1424,7 +1438,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
         <v>112</v>
       </c>
@@ -1443,7 +1457,7 @@
         <v>84</v>
       </c>
       <c r="H7" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I7" t="s" s="2">
         <v>75</v>
@@ -1521,21 +1535,21 @@
         <v>75</v>
       </c>
       <c r="AJ7" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK7" t="s" s="2">
         <v>118</v>
       </c>
-      <c r="AK7" t="s" s="2">
+      <c r="AL7" t="s" s="2">
         <v>119</v>
       </c>
-      <c r="AL7" t="s" s="2">
+    </row>
+    <row r="8" hidden="true">
+      <c r="A8" t="s" s="2">
         <v>120</v>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s" s="2">
-        <v>121</v>
-      </c>
       <c r="B8" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1558,16 +1572,16 @@
         <v>85</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="L8" t="s" s="2">
         <v>122</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="M8" t="s" s="2">
         <v>123</v>
       </c>
-      <c r="M8" t="s" s="2">
+      <c r="N8" t="s" s="2">
         <v>124</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>125</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -1617,7 +1631,7 @@
         <v>75</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>76</v>
@@ -1632,18 +1646,18 @@
         <v>96</v>
       </c>
       <c r="AK8" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="AL8" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="9" hidden="true">
+      <c r="A9" t="s" s="2">
         <v>126</v>
       </c>
-      <c r="AL8" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s" s="2">
-        <v>127</v>
-      </c>
       <c r="B9" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1657,7 +1671,7 @@
         <v>84</v>
       </c>
       <c r="H9" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I9" t="s" s="2">
         <v>75</v>
@@ -1666,16 +1680,16 @@
         <v>75</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="L9" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="M9" t="s" s="2">
         <v>129</v>
       </c>
-      <c r="M9" t="s" s="2">
+      <c r="N9" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>131</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -1725,7 +1739,7 @@
         <v>75</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>76</v>
@@ -1740,13 +1754,31 @@
         <v>96</v>
       </c>
       <c r="AK9" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="AL9" t="s" s="2">
         <v>132</v>
       </c>
-      <c r="AL9" t="s" s="2">
-        <v>133</v>
-      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AL9">
+    <filterColumn colId="6">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+    <filterColumn colId="26">
+      <filters blank="true"/>
+    </filterColumn>
+  </autoFilter>
+  <conditionalFormatting sqref="A2:AI8">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$G2&lt;&gt;"Y"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$Q2&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.14.0</t>
+    <t>0.15.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-13T13:47:03+00:00</t>
+    <t>2024-01-14T11:16:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.15.0</t>
+    <t>0.16.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-14T11:16:16+00:00</t>
+    <t>2024-02-08T09:36:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-08T09:36:20+00:00</t>
+    <t>2024-02-09T16:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-09T16:38:59+00:00</t>
+    <t>2024-02-11T14:24:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -384,7 +384,7 @@
     <t>ED.mediaType</t>
   </si>
   <si>
-    <t>++: fixed value = text/plain</t>
+    <t>1726: fixed value = text/plain</t>
   </si>
   <si>
     <t>Binary.securityContext</t>
@@ -425,7 +425,7 @@
     <t>ED.data</t>
   </si>
   <si>
-    <t>++: source value from TIU DOCUMENT - REPORT TEXT (#8925-2)</t>
+    <t>1725: source value from TIU DOCUMENT - REPORT TEXT (#8925-2)</t>
   </si>
 </sst>
 </file>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.16.0</t>
+    <t>0.17.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-11T14:24:24+00:00</t>
+    <t>2024-02-12T08:51:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.17.0</t>
+    <t>0.18.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T08:51:11+00:00</t>
+    <t>2024-02-13T17:27:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.18.0</t>
+    <t>0.19.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T17:27:52+00:00</t>
+    <t>2024-02-13T18:57:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T18:57:41+00:00</t>
+    <t>2024-02-13T19:55:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.19.0</t>
+    <t>0.20.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T19:55:01+00:00</t>
+    <t>2024-02-17T09:04:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.20.0</t>
+    <t>0.21.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:04:28+00:00</t>
+    <t>2024-02-17T09:43:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.21.0</t>
+    <t>0.22.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:43:43+00:00</t>
+    <t>2024-02-18T11:03:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="134">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.22.0</t>
+    <t>0.23.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-18T11:03:00+00:00</t>
+    <t>2024-02-23T15:31:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -372,6 +372,9 @@
     <t>MimeType of the binary content represented as a standard MimeType (BCP 13).</t>
   </si>
   <si>
+    <t>text/plain</t>
+  </si>
+  <si>
     <t>required</t>
   </si>
   <si>
@@ -384,7 +387,7 @@
     <t>ED.mediaType</t>
   </si>
   <si>
-    <t>1726: fixed value = text/plain</t>
+    <t>1726: fixed value = #text/plain</t>
   </si>
   <si>
     <t>Binary.securityContext</t>
@@ -1484,7 +1487,7 @@
         <v>75</v>
       </c>
       <c r="S7" t="s" s="2">
-        <v>75</v>
+        <v>115</v>
       </c>
       <c r="T7" t="s" s="2">
         <v>75</v>
@@ -1499,13 +1502,13 @@
         <v>75</v>
       </c>
       <c r="X7" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Y7" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Z7" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AA7" t="s" s="2">
         <v>75</v>
@@ -1538,18 +1541,18 @@
         <v>96</v>
       </c>
       <c r="AK7" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1572,16 +1575,16 @@
         <v>85</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -1631,7 +1634,7 @@
         <v>75</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>76</v>
@@ -1646,7 +1649,7 @@
         <v>96</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AL8" t="s" s="2">
         <v>75</v>
@@ -1654,10 +1657,10 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1680,16 +1683,16 @@
         <v>75</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -1739,7 +1742,7 @@
         <v>75</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>76</v>
@@ -1754,10 +1757,10 @@
         <v>96</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
   </sheetData>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.23.0</t>
+    <t>0.24.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-23T15:31:48+00:00</t>
+    <t>2024-02-28T12:35:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.24.0</t>
+    <t>0.26.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-28T12:35:36+00:00</t>
+    <t>2024-03-08T13:22:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.26.0</t>
+    <t>0.27.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T13:22:05+00:00</t>
+    <t>2024-03-08T18:48:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.27.0</t>
+    <t>0.28.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T18:48:53+00:00</t>
+    <t>2024-03-09T10:17:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.28.0</t>
+    <t>0.30.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-09T10:17:01+00:00</t>
+    <t>2024-03-21T09:40:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -237,10 +237,10 @@
     <t>Constraint(s)</t>
   </si>
   <si>
+    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
+  </si>
+  <si>
     <t>Mapping: RIM Mapping</t>
-  </si>
-  <si>
-    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
   </si>
   <si>
     <t/>
@@ -384,10 +384,10 @@
     <t>http://hl7.org/fhir/ValueSet/mimetypes|4.0.1</t>
   </si>
   <si>
+    <t>1726: fixed value = #text/plain</t>
+  </si>
+  <si>
     <t>ED.mediaType</t>
-  </si>
-  <si>
-    <t>1726: fixed value = #text/plain</t>
   </si>
   <si>
     <t>Binary.securityContext</t>
@@ -425,10 +425,10 @@
     <t>If the content type is itself base64 encoding, then this will be base64 encoded twice - what is created by un-base64ing the content must be the specified content type.</t>
   </si>
   <si>
+    <t>1725: source value from TIU DOCUMENT - REPORT TEXT (#8925-2)</t>
+  </si>
+  <si>
     <t>ED.data</t>
-  </si>
-  <si>
-    <t>1725: source value from TIU DOCUMENT - REPORT TEXT (#8925-2)</t>
   </si>
 </sst>
 </file>
@@ -783,8 +783,8 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="24.98046875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="88.6875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="88.6875" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="24.98046875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1005,10 +1005,10 @@
         <v>75</v>
       </c>
       <c r="AK2" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL2" t="s" s="2">
         <v>82</v>
-      </c>
-      <c r="AL2" t="s" s="2">
-        <v>75</v>
       </c>
     </row>
     <row r="3" hidden="true">
@@ -1649,10 +1649,10 @@
         <v>96</v>
       </c>
       <c r="AK8" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL8" t="s" s="2">
         <v>126</v>
-      </c>
-      <c r="AL8" t="s" s="2">
-        <v>75</v>
       </c>
     </row>
     <row r="9" hidden="true">

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.30.0</t>
+    <t>0.32.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-21T09:40:56+00:00</t>
+    <t>2024-03-22T16:04:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.32.0</t>
+    <t>0.34.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-22T16:04:14+00:00</t>
+    <t>2024-03-29T18:32:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-29T18:32:47+00:00</t>
+    <t>2024-03-30T09:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$9</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="135">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.34.0</t>
+    <t>0.36.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-30T09:34:15+00:00</t>
+    <t>2024-04-03T07:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -238,6 +238,9 @@
   </si>
   <si>
     <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
+  </si>
+  <si>
+    <t>Mapping: Clinical Data Warehouse (CDW)</t>
   </si>
   <si>
     <t>Mapping: RIM Mapping</t>
@@ -745,7 +748,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AL9"/>
+  <dimension ref="A1:AM9"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.05078125" customWidth="true" bestFit="true"/>
@@ -784,7 +787,8 @@
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="88.6875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="24.98046875" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="43.94140625" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="24.98046875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -902,6 +906,9 @@
       <c r="AL1" t="s" s="1">
         <v>74</v>
       </c>
+      <c r="AM1" t="s" s="1">
+        <v>75</v>
+      </c>
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
@@ -912,859 +919,883 @@
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H2" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I2" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J2" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K2" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L2" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M2" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="N2" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O2" s="2"/>
       <c r="P2" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Q2" s="2"/>
       <c r="R2" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="S2" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="T2" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="U2" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="V2" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="W2" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="X2" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Y2" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Z2" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AA2" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AB2" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AC2" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AD2" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AE2" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF2" t="s" s="2">
         <v>30</v>
       </c>
       <c r="AG2" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH2" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI2" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AK2" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AL2" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
+      </c>
+      <c r="AM2" t="s" s="2">
+        <v>83</v>
       </c>
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H3" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I3" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Q3" s="2"/>
       <c r="R3" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="S3" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="T3" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="U3" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="V3" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="W3" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="X3" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Y3" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Z3" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AA3" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AB3" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AC3" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AD3" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AE3" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI3" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AJ3" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AK3" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AL3" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="AM3" t="s" s="2">
+        <v>76</v>
       </c>
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H4" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I4" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
       <c r="P4" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Q4" s="2"/>
       <c r="R4" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="S4" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="T4" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="U4" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="V4" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="W4" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="X4" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Y4" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Z4" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AA4" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AB4" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AC4" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AD4" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AE4" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK4" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AL4" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="AM4" t="s" s="2">
+        <v>76</v>
       </c>
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H5" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Q5" s="2"/>
       <c r="R5" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="S5" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="T5" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="U5" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="V5" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="W5" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="X5" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Y5" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Z5" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AA5" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AB5" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AC5" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AD5" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AE5" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AL5" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="AM5" t="s" s="2">
+        <v>76</v>
       </c>
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H6" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I6" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J6" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Q6" s="2"/>
       <c r="R6" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="S6" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="T6" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="U6" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="V6" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="W6" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AA6" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AB6" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AC6" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AD6" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AL6" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="AM6" t="s" s="2">
+        <v>76</v>
       </c>
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H7" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I7" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Q7" s="2"/>
       <c r="R7" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="S7" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="T7" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="U7" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="V7" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="W7" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="X7" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Y7" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Z7" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AA7" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AB7" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AC7" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AD7" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AE7" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK7" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>120</v>
+        <v>76</v>
+      </c>
+      <c r="AM7" t="s" s="2">
+        <v>121</v>
       </c>
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H8" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I8" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Q8" s="2"/>
       <c r="R8" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="S8" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="T8" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="U8" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="V8" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="W8" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="X8" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Y8" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Z8" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AA8" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AB8" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AC8" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AD8" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AE8" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI8" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>126</v>
+        <v>76</v>
+      </c>
+      <c r="AM8" t="s" s="2">
+        <v>127</v>
       </c>
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H9" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I9" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="S9" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="T9" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="U9" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="V9" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="W9" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="X9" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Y9" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Z9" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AA9" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AC9" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AD9" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AG9" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>133</v>
+        <v>76</v>
+      </c>
+      <c r="AM9" t="s" s="2">
+        <v>134</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AL9">
+  <autoFilter ref="A1:AM9">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T07:33:38+00:00</t>
+    <t>2024-04-03T08:58:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T08:58:56+00:00</t>
+    <t>2024-04-10T18:17:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file TIU DOCUMENT (#8925) to Binary</t>
+    <t>This StructureDefinition contains the maps for VistA file TIU DOCUMENT (8925) to Binary</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -428,7 +428,7 @@
     <t>If the content type is itself base64 encoding, then this will be base64 encoded twice - what is created by un-base64ing the content must be the specified content type.</t>
   </si>
   <si>
-    <t>1725: source value from TIU DOCUMENT - REPORT TEXT (#8925-2)</t>
+    <t>1725: source value from TIU DOCUMENT - REPORT TEXT (8925-2)</t>
   </si>
   <si>
     <t>ED.data</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.36.0</t>
+    <t>0.37.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T18:17:58+00:00</t>
+    <t>2024-04-10T21:21:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.37.0</t>
+    <t>0.38.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T21:21:54+00:00</t>
+    <t>2024-04-12T10:04:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>VA (https://www.va.gov)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.38.0</t>
+    <t>0.39.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T10:04:01+00:00</t>
+    <t>2024-04-12T16:57:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.39.0</t>
+    <t>0.40.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T16:57:46+00:00</t>
+    <t>2024-04-13T07:20:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.40.0</t>
+    <t>0.41.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-13T07:20:06+00:00</t>
+    <t>2024-04-21T15:38:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.41.0</t>
+    <t>0.42.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-21T15:38:45+00:00</t>
+    <t>2024-04-22T07:04:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.42.0</t>
+    <t>0.43.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T07:04:34+00:00</t>
+    <t>2024-04-24T08:47:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.43.0</t>
+    <t>0.44.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-24T08:47:54+00:00</t>
+    <t>2024-04-25T08:17:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.44.0</t>
+    <t>0.45.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-25T08:17:47+00:00</t>
+    <t>2024-05-01T09:37:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.45.0</t>
+    <t>0.46.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T09:37:14+00:00</t>
+    <t>2024-05-01T10:34:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.46.0</t>
+    <t>0.47.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T10:34:27+00:00</t>
+    <t>2024-05-04T09:18:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.47.0</t>
+    <t>0.48.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-04T09:18:00+00:00</t>
+    <t>2024-05-06T08:00:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.48.0</t>
+    <t>0.49.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T08:00:03+00:00</t>
+    <t>2024-05-06T11:38:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.49.0</t>
+    <t>0.50.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T11:38:53+00:00</t>
+    <t>2024-05-08T06:31:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.50.0</t>
+    <t>0.51.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-08T06:31:45+00:00</t>
+    <t>2024-05-11T08:27:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.51.0</t>
+    <t>0.52.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-11T08:27:40+00:00</t>
+    <t>2024-05-19T08:28:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -428,7 +428,7 @@
     <t>If the content type is itself base64 encoding, then this will be base64 encoded twice - what is created by un-base64ing the content must be the specified content type.</t>
   </si>
   <si>
-    <t>1725: source value from TIU DOCUMENT - REPORT TEXT (8925-2)</t>
+    <t>1725-1: fixed value without value?</t>
   </si>
   <si>
     <t>ED.data</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.52.0</t>
+    <t>0.53.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-19T08:28:17+00:00</t>
+    <t>2024-05-22T14:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.53.0</t>
+    <t>0.54.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-22T14:44:53+00:00</t>
+    <t>2024-05-25T10:26:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.54.0</t>
+    <t>0.57.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-25T10:26:15+00:00</t>
+    <t>2024-06-04T15:52:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-04T15:52:07+00:00</t>
+    <t>2024-06-11T05:38:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T05:38:55+00:00</t>
+    <t>2024-06-12T18:51:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.57.0</t>
+    <t>0.58.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-12T18:51:20+00:00</t>
+    <t>2024-06-14T11:56:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.58.0</t>
+    <t>0.59.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-14T11:56:40+00:00</t>
+    <t>2024-06-21T15:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-21T15:05:18+00:00</t>
+    <t>2024-07-09T16:26:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.59.0</t>
+    <t>0.61.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-09T16:26:13+00:00</t>
+    <t>2024-07-24T18:59:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.61.0</t>
+    <t>0.62.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-24T18:59:55+00:00</t>
+    <t>2024-07-28T09:11:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.62.0</t>
+    <t>0.63.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-28T09:11:13+00:00</t>
+    <t>2024-07-31T09:58:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.63.0</t>
+    <t>0.64.311</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T09:58:27+00:00</t>
+    <t>2024-07-31T19:09:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.311</t>
+    <t>0.64.312</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T19:09:08+00:00</t>
+    <t>2024-08-02T13:01:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.312</t>
+    <t>0.64.316</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-02T13:01:18+00:00</t>
+    <t>2024-08-04T09:05:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.316</t>
+    <t>0.64.318</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-04T09:05:29+00:00</t>
+    <t>2024-08-05T15:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.318</t>
+    <t>0.65.329</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-05T15:01:43+00:00</t>
+    <t>2024-08-13T08:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.329</t>
+    <t>0.65.332</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T08:01:15+00:00</t>
+    <t>2024-08-13T15:06:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.332</t>
+    <t>0.65.334</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T15:06:38+00:00</t>
+    <t>2024-08-14T15:16:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-14T15:16:17+00:00</t>
+    <t>2024-08-17T06:29:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.334</t>
+    <t>0.65.339</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-17T06:29:49+00:00</t>
+    <t>2024-08-18T10:15:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.339</t>
+    <t>0.65.341</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-18T10:15:47+00:00</t>
+    <t>2024-08-20T15:42:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.341</t>
+    <t>0.65.343</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-20T15:42:57+00:00</t>
+    <t>2024-08-24T10:06:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.343</t>
+    <t>0.65.345</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-24T10:06:05+00:00</t>
+    <t>2024-08-26T15:27:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.345</t>
+    <t>0.65.348</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-26T15:27:18+00:00</t>
+    <t>2024-09-15T08:33:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.348</t>
+    <t>0.66.354</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-15T08:33:43+00:00</t>
+    <t>2024-09-19T08:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.354</t>
+    <t>0.66.364</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-19T08:45:12+00:00</t>
+    <t>2024-10-02T18:53:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.364</t>
+    <t>0.66.366</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-02T18:53:29+00:00</t>
+    <t>2024-10-11T07:57:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.366</t>
+    <t>0.66.367</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-11T07:57:28+00:00</t>
+    <t>2024-10-13T09:59:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.367</t>
+    <t>0.67.369</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-13T09:59:39+00:00</t>
+    <t>2024-10-18T16:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.369</t>
+    <t>0.67.370</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T16:05:33+00:00</t>
+    <t>2024-10-20T09:02:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.370</t>
+    <t>0.67.378</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-20T09:02:32+00:00</t>
+    <t>2024-10-30T12:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -387,7 +387,7 @@
     <t>http://hl7.org/fhir/ValueSet/mimetypes|4.0.1</t>
   </si>
   <si>
-    <t>1726: fixed value = #text/plain</t>
+    <t>1725-1: fixed value = #text/plain</t>
   </si>
   <si>
     <t>ED.mediaType</t>
@@ -428,7 +428,7 @@
     <t>If the content type is itself base64 encoding, then this will be base64 encoded twice - what is created by un-base64ing the content must be the specified content type.</t>
   </si>
   <si>
-    <t>1725-1: fixed value without value?</t>
+    <t>1725: source value from TIU DOCUMENT - REPORT TEXT (8925-2)</t>
   </si>
   <si>
     <t>ED.data</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.378</t>
+    <t>0.67.381</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T12:26:51+00:00</t>
+    <t>2024-11-03T11:50:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.381</t>
+    <t>0.68.397</t>
   </si>
   <si>
     <t>Name</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-03T11:50:46+00:00</t>
+    <t>2024-11-10T10:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.397</t>
+    <t>0.68.401</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-10T10:13:24+00:00</t>
+    <t>2024-11-13T21:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.401</t>
+    <t>0.68.419</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-13T21:40:45+00:00</t>
+    <t>2024-11-25T07:50:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.419</t>
+    <t>0.68.424</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-25T07:50:24+00:00</t>
+    <t>2024-11-30T14:03:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.424</t>
+    <t>0.68.425</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T14:03:16+00:00</t>
+    <t>2024-11-30T15:07:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$9</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="134">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.425</t>
+    <t>0.69.436</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T15:07:22+00:00</t>
+    <t>2024-12-04T11:34:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -238,9 +238,6 @@
   </si>
   <si>
     <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
-  </si>
-  <si>
-    <t>Mapping: Clinical Data Warehouse (CDW)</t>
   </si>
   <si>
     <t>Mapping: RIM Mapping</t>
@@ -748,7 +745,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AM9"/>
+  <dimension ref="A1:AL9"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.05078125" customWidth="true" bestFit="true"/>
@@ -787,8 +784,7 @@
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="88.6875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="43.94140625" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="24.98046875" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="24.98046875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -906,9 +902,6 @@
       <c r="AL1" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="AM1" t="s" s="1">
-        <v>75</v>
-      </c>
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
@@ -919,883 +912,859 @@
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G2" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="G2" t="s" s="2">
+      <c r="H2" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I2" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J2" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K2" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="H2" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I2" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J2" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="K2" t="s" s="2">
+      <c r="L2" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="L2" t="s" s="2">
+      <c r="M2" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="M2" t="s" s="2">
+      <c r="N2" t="s" s="2">
         <v>81</v>
-      </c>
-      <c r="N2" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="O2" s="2"/>
       <c r="P2" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Q2" s="2"/>
       <c r="R2" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="S2" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="T2" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="U2" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="V2" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="W2" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="X2" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Y2" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Z2" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AA2" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AB2" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AC2" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AD2" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AE2" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AF2" t="s" s="2">
         <v>30</v>
       </c>
       <c r="AG2" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH2" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="AH2" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="AI2" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AK2" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AL2" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM2" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G3" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H3" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I3" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J3" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="H3" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I3" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J3" t="s" s="2">
+      <c r="K3" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="K3" t="s" s="2">
+      <c r="L3" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="L3" t="s" s="2">
+      <c r="M3" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="M3" t="s" s="2">
+      <c r="N3" t="s" s="2">
         <v>89</v>
-      </c>
-      <c r="N3" t="s" s="2">
-        <v>90</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Q3" s="2"/>
       <c r="R3" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S3" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T3" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U3" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V3" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W3" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X3" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y3" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z3" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA3" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB3" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC3" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD3" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE3" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF3" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AG3" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="S3" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="T3" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U3" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V3" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W3" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X3" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y3" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z3" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA3" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB3" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC3" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD3" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE3" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF3" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AG3" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="AH3" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI3" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AJ3" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AK3" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AL3" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM3" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G4" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H4" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I4" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J4" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="H4" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I4" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J4" t="s" s="2">
-        <v>86</v>
-      </c>
       <c r="K4" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="L4" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="L4" t="s" s="2">
+      <c r="M4" t="s" s="2">
         <v>94</v>
-      </c>
-      <c r="M4" t="s" s="2">
-        <v>95</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
       <c r="P4" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Q4" s="2"/>
       <c r="R4" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S4" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T4" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U4" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V4" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W4" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X4" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y4" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z4" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA4" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB4" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC4" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD4" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE4" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF4" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AG4" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="S4" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="T4" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U4" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V4" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W4" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X4" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y4" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z4" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA4" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB4" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC4" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD4" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE4" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF4" t="s" s="2">
+      <c r="AH4" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI4" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ4" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AG4" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH4" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI4" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ4" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="AK4" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AL4" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM4" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G5" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H5" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I5" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="H5" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I5" t="s" s="2">
-        <v>86</v>
-      </c>
       <c r="J5" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K5" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="L5" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="L5" t="s" s="2">
+      <c r="M5" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="M5" t="s" s="2">
+      <c r="N5" t="s" s="2">
         <v>101</v>
-      </c>
-      <c r="N5" t="s" s="2">
-        <v>102</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Q5" s="2"/>
       <c r="R5" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S5" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T5" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U5" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V5" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W5" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X5" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y5" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z5" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA5" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB5" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC5" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD5" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE5" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF5" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AG5" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="S5" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="T5" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U5" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V5" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W5" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X5" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y5" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z5" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA5" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB5" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC5" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD5" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE5" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF5" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AG5" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="AH5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AL5" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM5" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H6" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I6" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J6" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L6" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="L6" t="s" s="2">
+      <c r="M6" t="s" s="2">
         <v>106</v>
       </c>
-      <c r="M6" t="s" s="2">
+      <c r="N6" t="s" s="2">
         <v>107</v>
-      </c>
-      <c r="N6" t="s" s="2">
-        <v>108</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Q6" s="2"/>
       <c r="R6" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S6" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T6" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U6" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V6" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W6" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X6" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="Y6" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="Z6" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="AA6" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB6" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD6" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE6" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF6" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="AG6" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="S6" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="T6" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U6" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V6" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W6" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X6" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="Y6" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="Z6" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="AA6" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD6" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF6" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="AG6" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="AH6" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AL6" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM6" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="G7" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H7" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="G7" t="s" s="2">
+      <c r="I7" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J7" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="H7" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="I7" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J7" t="s" s="2">
-        <v>86</v>
-      </c>
       <c r="K7" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L7" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="M7" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="M7" t="s" s="2">
-        <v>115</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Q7" s="2"/>
       <c r="R7" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="S7" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="T7" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U7" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V7" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W7" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X7" t="s" s="2">
         <v>116</v>
       </c>
-      <c r="T7" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U7" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V7" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W7" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X7" t="s" s="2">
+      <c r="Y7" t="s" s="2">
         <v>117</v>
       </c>
-      <c r="Y7" t="s" s="2">
+      <c r="Z7" t="s" s="2">
         <v>118</v>
       </c>
-      <c r="Z7" t="s" s="2">
+      <c r="AA7" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB7" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC7" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD7" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE7" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF7" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="AG7" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AH7" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI7" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ7" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK7" t="s" s="2">
         <v>119</v>
       </c>
-      <c r="AA7" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB7" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC7" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD7" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE7" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF7" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="AG7" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH7" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI7" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ7" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AK7" t="s" s="2">
+      <c r="AL7" t="s" s="2">
         <v>120</v>
-      </c>
-      <c r="AL7" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM7" t="s" s="2">
-        <v>121</v>
       </c>
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G8" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H8" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I8" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J8" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="H8" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I8" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J8" t="s" s="2">
-        <v>86</v>
-      </c>
       <c r="K8" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="L8" t="s" s="2">
         <v>123</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="M8" t="s" s="2">
         <v>124</v>
       </c>
-      <c r="M8" t="s" s="2">
+      <c r="N8" t="s" s="2">
         <v>125</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>126</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Q8" s="2"/>
       <c r="R8" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S8" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T8" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U8" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V8" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W8" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X8" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y8" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z8" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA8" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB8" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC8" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD8" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE8" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF8" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="AG8" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="S8" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="T8" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U8" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V8" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W8" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X8" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y8" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z8" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA8" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB8" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC8" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD8" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE8" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF8" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="AG8" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="AH8" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI8" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM8" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G9" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H9" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="H9" t="s" s="2">
-        <v>86</v>
-      </c>
       <c r="I9" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="L9" t="s" s="2">
         <v>129</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="M9" t="s" s="2">
         <v>130</v>
       </c>
-      <c r="M9" t="s" s="2">
+      <c r="N9" t="s" s="2">
         <v>131</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>132</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S9" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T9" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U9" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V9" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W9" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X9" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y9" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z9" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA9" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB9" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC9" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD9" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE9" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF9" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="AG9" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="S9" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="T9" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U9" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V9" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W9" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X9" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y9" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z9" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA9" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB9" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC9" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD9" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE9" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF9" t="s" s="2">
-        <v>128</v>
-      </c>
-      <c r="AG9" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="AH9" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AK9" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AL9" t="s" s="2">
         <v>133</v>
       </c>
-      <c r="AL9" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM9" t="s" s="2">
-        <v>134</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AM9">
+  <autoFilter ref="A1:AL9">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$9</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="136">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.436</t>
+    <t>0.69.437</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T11:34:53+00:00</t>
+    <t>2024-12-04T16:25:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -238,6 +238,9 @@
   </si>
   <si>
     <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
+  </si>
+  <si>
+    <t>Mapping: Virtual Patient Record (VPR)</t>
   </si>
   <si>
     <t>Mapping: RIM Mapping</t>
@@ -426,6 +429,9 @@
   </si>
   <si>
     <t>1725: source value from TIU DOCUMENT - REPORT TEXT (8925-2)</t>
+  </si>
+  <si>
+    <t>document.content[n]</t>
   </si>
   <si>
     <t>ED.data</t>
@@ -745,7 +751,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AL9"/>
+  <dimension ref="A1:AM9"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.05078125" customWidth="true" bestFit="true"/>
@@ -784,7 +790,8 @@
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="88.6875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="24.98046875" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="40.984375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="24.98046875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -902,6 +909,9 @@
       <c r="AL1" t="s" s="1">
         <v>74</v>
       </c>
+      <c r="AM1" t="s" s="1">
+        <v>75</v>
+      </c>
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
@@ -912,859 +922,883 @@
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H2" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I2" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J2" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K2" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L2" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M2" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="N2" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O2" s="2"/>
       <c r="P2" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Q2" s="2"/>
       <c r="R2" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="S2" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="T2" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="U2" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="V2" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="W2" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="X2" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Y2" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Z2" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AA2" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AB2" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AC2" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AD2" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AE2" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF2" t="s" s="2">
         <v>30</v>
       </c>
       <c r="AG2" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH2" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI2" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AK2" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AL2" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
+      </c>
+      <c r="AM2" t="s" s="2">
+        <v>83</v>
       </c>
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H3" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I3" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Q3" s="2"/>
       <c r="R3" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="S3" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="T3" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="U3" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="V3" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="W3" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="X3" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Y3" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Z3" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AA3" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AB3" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AC3" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AD3" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AE3" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI3" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AJ3" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AK3" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AL3" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="AM3" t="s" s="2">
+        <v>76</v>
       </c>
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H4" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I4" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
       <c r="P4" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Q4" s="2"/>
       <c r="R4" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="S4" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="T4" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="U4" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="V4" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="W4" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="X4" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Y4" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Z4" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AA4" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AB4" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AC4" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AD4" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AE4" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK4" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AL4" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="AM4" t="s" s="2">
+        <v>76</v>
       </c>
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H5" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Q5" s="2"/>
       <c r="R5" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="S5" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="T5" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="U5" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="V5" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="W5" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="X5" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Y5" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Z5" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AA5" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AB5" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AC5" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AD5" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AE5" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AL5" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="AM5" t="s" s="2">
+        <v>76</v>
       </c>
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H6" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I6" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J6" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Q6" s="2"/>
       <c r="R6" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="S6" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="T6" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="U6" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="V6" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="W6" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AA6" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AB6" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AC6" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AD6" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AL6" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="AM6" t="s" s="2">
+        <v>76</v>
       </c>
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H7" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I7" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Q7" s="2"/>
       <c r="R7" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="S7" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="T7" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="U7" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="V7" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="W7" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="X7" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Y7" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Z7" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AA7" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AB7" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AC7" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AD7" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AE7" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK7" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>120</v>
+        <v>76</v>
+      </c>
+      <c r="AM7" t="s" s="2">
+        <v>121</v>
       </c>
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H8" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I8" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Q8" s="2"/>
       <c r="R8" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="S8" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="T8" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="U8" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="V8" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="W8" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="X8" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Y8" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Z8" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AA8" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AB8" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AC8" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AD8" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AE8" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI8" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>126</v>
+        <v>76</v>
+      </c>
+      <c r="AM8" t="s" s="2">
+        <v>127</v>
       </c>
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H9" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I9" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="S9" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="T9" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="U9" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="V9" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="W9" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="X9" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Y9" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Z9" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AA9" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AC9" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AD9" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AG9" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
+      </c>
+      <c r="AM9" t="s" s="2">
+        <v>135</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AL9">
+  <autoFilter ref="A1:AM9">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.437</t>
+    <t>0.69.438</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T16:25:11+00:00</t>
+    <t>2024-12-06T17:18:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -240,7 +240,7 @@
     <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
   </si>
   <si>
-    <t>Mapping: Virtual Patient Record (VPR)</t>
+    <t>Mapping: Summary Document Architecure (SDA)</t>
   </si>
   <si>
     <t>Mapping: RIM Mapping</t>
@@ -790,7 +790,7 @@
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="88.6875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="40.984375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="51.63671875" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="24.98046875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.438</t>
+    <t>0.69.439</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-06T17:18:58+00:00</t>
+    <t>2024-12-07T11:18:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -431,7 +431,7 @@
     <t>1725: source value from TIU DOCUMENT - REPORT TEXT (8925-2)</t>
   </si>
   <si>
-    <t>document.content[n]</t>
+    <t>Alert.Comments,Documents.NoteText,AdvanceDirective.Comments</t>
   </si>
   <si>
     <t>ED.data</t>
@@ -790,7 +790,7 @@
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="88.6875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="51.63671875" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="63.21875" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="24.98046875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.439</t>
+    <t>0.69.440</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-07T11:18:15+00:00</t>
+    <t>2024-12-08T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -431,7 +431,7 @@
     <t>1725: source value from TIU DOCUMENT - REPORT TEXT (8925-2)</t>
   </si>
   <si>
-    <t>Alert.Comments,Documents.NoteText,AdvanceDirective.Comments</t>
+    <t>AdvanceDirective.Comments,Alert.Comments,Documents.NoteText</t>
   </si>
   <si>
     <t>ED.data</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.440</t>
+    <t>0.69.442</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-08T09:28:43+00:00</t>
+    <t>2024-12-11T20:06:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.442</t>
+    <t>0.69.448</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T20:06:32+00:00</t>
+    <t>2024-12-21T10:24:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file TIU DOCUMENT (8925) to Binary</t>
+    <t>This StructureDefinition contains the maps for VistA file TIU DOCUMENT (8925) to Binary.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.448</t>
+    <t>1.1.467</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-21T10:24:25+00:00</t>
+    <t>2025-01-04T09:38:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.467</t>
+    <t>1.1.468</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T09:38:39+00:00</t>
+    <t>2025-01-04T15:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.468</t>
+    <t>1.1.477</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T15:04:27+00:00</t>
+    <t>2025-01-07T16:27:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.477</t>
+    <t>1.1.478</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T16:27:08+00:00</t>
+    <t>2025-01-13T09:39:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.478</t>
+    <t>1.1.487</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-13T09:39:57+00:00</t>
+    <t>2025-01-17T12:09:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -428,7 +428,7 @@
     <t>If the content type is itself base64 encoding, then this will be base64 encoded twice - what is created by un-base64ing the content must be the specified content type.</t>
   </si>
   <si>
-    <t>1725: source value from TIU DOCUMENT - REPORT TEXT (8925-2)</t>
+    <t>1725: source value based on TIU DOCUMENT - REPORT TEXT (8925-2)</t>
   </si>
   <si>
     <t>AdvanceDirective.Comments,Alert.Comments,Documents.NoteText</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.487</t>
+    <t>1.1.491</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T12:09:20+00:00</t>
+    <t>2025-01-17T13:37:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.491</t>
+    <t>1.1.494</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T13:37:46+00:00</t>
+    <t>2025-01-25T09:28:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.494</t>
+    <t>1.1.500</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-25T09:28:03+00:00</t>
+    <t>2025-02-01T09:13:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.500</t>
+    <t>1.2.512</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-01T09:13:38+00:00</t>
+    <t>2025-02-05T16:47:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T16:47:13+00:00</t>
+    <t>2025-02-05T17:20:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.512</t>
+    <t>1.2.520</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T17:20:26+00:00</t>
+    <t>2025-02-08T12:00:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.520</t>
+    <t>1.2.529</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-08T12:00:09+00:00</t>
+    <t>2025-02-20T14:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.529</t>
+    <t>1.2.531</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:56:35+00:00</t>
+    <t>2025-02-22T09:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.531</t>
+    <t>1.2.537</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-22T09:54:59+00:00</t>
+    <t>2025-02-24T13:20:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:20:37+00:00</t>
+    <t>2025-02-25T20:49:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.537</t>
+    <t>1.2.540</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-25T20:49:13+00:00</t>
+    <t>2025-03-11T10:08:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.540</t>
+    <t>1.3.557</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T10:08:33+00:00</t>
+    <t>2025-03-15T09:48:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.557</t>
+    <t>1.3.574</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-15T09:48:09+00:00</t>
+    <t>2025-03-22T10:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.574</t>
+    <t>1.3.575</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:33:38+00:00</t>
+    <t>2025-03-22T10:56:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.575</t>
+    <t>1.3.578</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:56:07+00:00</t>
+    <t>2025-03-23T10:22:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.578</t>
+    <t>1.3.580</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T10:22:17+00:00</t>
+    <t>2025-03-23T13:19:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DocumentReferenceBinary.xlsx
+++ b/docs/StructureDefinition-DocumentReferenceBinary.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.580</t>
+    <t>1.4.588</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T13:19:29+00:00</t>
+    <t>2025-04-01T14:43:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
